--- a/artfynd/A 55246-2020 artfynd.xlsx
+++ b/artfynd/A 55246-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55246-2020 artfynd.xlsx
+++ b/artfynd/A 55246-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,327 +1375,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112605281</v>
-      </c>
-      <c r="B8" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Spikberg, Nb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>752844</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7339319</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Edefors</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112605280</v>
-      </c>
-      <c r="B9" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Spikberg, Nb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>752926</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7339347</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Edefors</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112605282</v>
-      </c>
-      <c r="B10" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Spikberg, Nb</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>752838</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7339304</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Edefors</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
